--- a/clustering/sepsectors/sector analysis (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/sector analysis (VDS_s) 0.xlsx
@@ -5,27 +5,27 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Albert\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Albert\.spyder-py3\ITMO-3\clustering\sepsectors\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Пром. производство" sheetId="3" r:id="rId1"/>
-    <sheet name="Сельхоз" sheetId="1" r:id="rId2"/>
-    <sheet name="Административный" sheetId="2" r:id="rId3"/>
-    <sheet name="Логистика" sheetId="4" r:id="rId4"/>
-    <sheet name="Добыча" sheetId="5" r:id="rId5"/>
-    <sheet name="Торговля" sheetId="6" r:id="rId6"/>
-    <sheet name="Наука" sheetId="7" r:id="rId7"/>
+    <sheet name="Логистика" sheetId="4" r:id="rId2"/>
+    <sheet name="Наука" sheetId="7" r:id="rId3"/>
+    <sheet name="Торговля" sheetId="6" r:id="rId4"/>
+    <sheet name="Сельхоз" sheetId="1" r:id="rId5"/>
+    <sheet name="Административный" sheetId="2" r:id="rId6"/>
+    <sheet name="Добыча" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="93">
   <si>
     <t>sector</t>
   </si>
@@ -395,7 +395,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -408,9 +408,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1454,13 +1451,13 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="7">
         <v>2023</v>
       </c>
       <c r="D32" s="3">
@@ -2167,7 +2164,7 @@
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D64" s="3">
@@ -2176,10 +2173,10 @@
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B65" s="7"/>
+      <c r="B65" s="6"/>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D66" s="3">
@@ -2200,7 +2197,7 @@
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D67" s="3">
@@ -2221,7 +2218,7 @@
       </c>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C69" s="7" t="s">
+      <c r="C69" s="6" t="s">
         <v>52</v>
       </c>
       <c r="D69" s="3">
@@ -2344,825 +2341,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="97.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D2" s="3">
-        <v>3292837.3871137551</v>
-      </c>
-      <c r="E2" s="3">
-        <v>5258.5701260400001</v>
-      </c>
-      <c r="F2" s="4">
-        <v>1.0604360748915839E-2</v>
-      </c>
-      <c r="G2" s="4">
-        <v>1.868819729404374E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D3" s="3">
-        <v>3097084.3107878752</v>
-      </c>
-      <c r="E3" s="3">
-        <v>4162.4721680000002</v>
-      </c>
-      <c r="F3" s="4">
-        <v>1.4081114307645259E-3</v>
-      </c>
-      <c r="G3" s="4">
-        <v>3.9573959548935052E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2652658.7944572391</v>
-      </c>
-      <c r="E4" s="3">
-        <v>4253.6615775199998</v>
-      </c>
-      <c r="F4" s="4">
-        <v>2.8806641846538372E-3</v>
-      </c>
-      <c r="G4" s="4">
-        <v>1.8380008135386839E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2480166.278394436</v>
-      </c>
-      <c r="E5" s="3">
-        <v>4510.0316159999993</v>
-      </c>
-      <c r="F5" s="4">
-        <v>1.003512255644462E-3</v>
-      </c>
-      <c r="G5" s="4">
-        <v>1.2206708220113729E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D6" s="3">
-        <v>331647.0310656284</v>
-      </c>
-      <c r="E6" s="3">
-        <v>964.84556195999994</v>
-      </c>
-      <c r="F6" s="4">
-        <v>7.4163848413873461E-4</v>
-      </c>
-      <c r="G6" s="4">
-        <v>3.6380912535570372E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D7" s="3">
-        <v>255261.79722573471</v>
-      </c>
-      <c r="E7" s="3">
-        <v>888.20773440000005</v>
-      </c>
-      <c r="F7" s="4">
-        <v>1.2066660967819649E-3</v>
-      </c>
-      <c r="G7" s="4">
-        <v>2.863735386990569E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D8" s="3">
-        <v>238996.75153477999</v>
-      </c>
-      <c r="E8" s="3">
-        <v>863.40619829999991</v>
-      </c>
-      <c r="F8" s="4">
-        <v>7.0023981897559661E-4</v>
-      </c>
-      <c r="G8" s="4">
-        <v>9.1753228267274999E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D9" s="3">
-        <v>218314.63160777459</v>
-      </c>
-      <c r="E9" s="3">
-        <v>897.65553599999998</v>
-      </c>
-      <c r="F9" s="4">
-        <v>4.6312642581418888E-4</v>
-      </c>
-      <c r="G9" s="4">
-        <v>5.3328786021100191E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D10" s="3">
-        <v>177476.11420904889</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1454.99992092</v>
-      </c>
-      <c r="F10" s="4">
-        <v>2.7347370558508639E-4</v>
-      </c>
-      <c r="G10" s="4">
-        <v>8.7625687236728058E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D11" s="3">
-        <v>149725.9222474432</v>
-      </c>
-      <c r="E11" s="3">
-        <v>1319.2765561000001</v>
-      </c>
-      <c r="F11" s="4">
-        <v>9.5143491498901212E-3</v>
-      </c>
-      <c r="G11" s="4">
-        <v>8.6555389370039323E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D12" s="3">
-        <v>123407.0292947656</v>
-      </c>
-      <c r="E12" s="3">
-        <v>769.72569599999997</v>
-      </c>
-      <c r="F12" s="4">
-        <v>1.643806367093142E-3</v>
-      </c>
-      <c r="G12" s="4">
-        <v>4.963035559098705E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D13" s="3">
-        <v>118648.02708896549</v>
-      </c>
-      <c r="E13" s="3">
-        <v>640.62859736000007</v>
-      </c>
-      <c r="F13" s="4">
-        <v>4.2703506076277667E-2</v>
-      </c>
-      <c r="G13" s="4">
-        <v>7.645975624855611E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="3">
-        <f>MEDIAN(D2:D13)</f>
-        <v>247129.27438025735</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="7"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="3">
-        <f>AVERAGE(D2:D7)</f>
-        <v>2018275.9331741116</v>
-      </c>
-      <c r="E17" s="3">
-        <f t="shared" ref="E17:G17" si="0">AVERAGE(E2:E7)</f>
-        <v>3339.6314639866664</v>
-      </c>
-      <c r="F17" s="4">
-        <f t="shared" si="0"/>
-        <v>2.974158866816561E-3</v>
-      </c>
-      <c r="G17" s="4">
-        <f t="shared" si="0"/>
-        <v>2.0187386386990346E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="3">
-        <f>AVERAGE(D8:D13)</f>
-        <v>171094.74599712962</v>
-      </c>
-      <c r="E18" s="3">
-        <f t="shared" ref="E18:G18" si="1">AVERAGE(E8:E13)</f>
-        <v>990.94875077999995</v>
-      </c>
-      <c r="F18" s="4">
-        <f t="shared" si="1"/>
-        <v>9.2164169239392999E-3</v>
-      </c>
-      <c r="G18" s="4">
-        <f t="shared" si="1"/>
-        <v>3.4335388058007936E-3</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState ref="A2:G13">
-    <sortCondition descending="1" ref="D2:D13"/>
-  </sortState>
-  <conditionalFormatting sqref="D2:D13">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D17:D18">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E17:E18">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17:F18">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="73" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D2" s="3">
-        <v>971947.1589226143</v>
-      </c>
-      <c r="E2" s="3">
-        <v>21731.663739110001</v>
-      </c>
-      <c r="F2" s="4">
-        <v>3.0282081846115981E-5</v>
-      </c>
-      <c r="G2" s="4">
-        <v>5.0206173563068553E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D3" s="3">
-        <v>950234.48563991196</v>
-      </c>
-      <c r="E3" s="3">
-        <v>3253.0570836699999</v>
-      </c>
-      <c r="F3" s="4">
-        <v>3.2666995157709352E-4</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1.167450820049999E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D4" s="3">
-        <v>840420.70663642394</v>
-      </c>
-      <c r="E4" s="3">
-        <v>22097.462448999999</v>
-      </c>
-      <c r="F4" s="4">
-        <v>1.047846559460851E-5</v>
-      </c>
-      <c r="G4" s="4">
-        <v>8.9257472528899238E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D5" s="3">
-        <v>130071.2900498806</v>
-      </c>
-      <c r="E5" s="3">
-        <v>866.32844524999996</v>
-      </c>
-      <c r="F5" s="4">
-        <v>1.8830176464184379E-3</v>
-      </c>
-      <c r="G5" s="4">
-        <v>2.5735129813919731E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D6" s="3">
-        <v>118956.3612196709</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1090.8420791399999</v>
-      </c>
-      <c r="F6" s="4">
-        <v>6.857037460360029E-4</v>
-      </c>
-      <c r="G6" s="4">
-        <v>4.8025762850386331E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D7" s="3">
-        <v>106346.7598437235</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1736.36278023</v>
-      </c>
-      <c r="F7" s="4">
-        <v>2.7534118528886658E-3</v>
-      </c>
-      <c r="G7" s="4">
-        <v>9.5257384161442811E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D8" s="3">
-        <v>85809.083743767143</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2740.6294030899999</v>
-      </c>
-      <c r="F8" s="4">
-        <v>3.444045779906578E-2</v>
-      </c>
-      <c r="G8" s="4">
-        <v>2.7573625574766692E-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="3">
-        <f>MEDIAN(D2:D8)</f>
-        <v>130071.2900498806</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="3">
-        <f>AVERAGE(D2:D4)</f>
-        <v>920867.45039964991</v>
-      </c>
-      <c r="E12" s="3">
-        <f t="shared" ref="E12:G12" si="0">AVERAGE(E2:E4)</f>
-        <v>15694.061090593334</v>
-      </c>
-      <c r="F12" s="4">
-        <f t="shared" si="0"/>
-        <v>1.2247683300593934E-4</v>
-      </c>
-      <c r="G12" s="4">
-        <f t="shared" si="0"/>
-        <v>5.0379384764155924E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="3">
-        <f>AVERAGE(D6:D8)</f>
-        <v>103704.06826905387</v>
-      </c>
-      <c r="E13" s="3">
-        <f t="shared" ref="E13:G13" si="1">AVERAGE(E6:E8)</f>
-        <v>1855.9447541533334</v>
-      </c>
-      <c r="F13" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2626524465996816E-2</v>
-      </c>
-      <c r="G13" s="4">
-        <f t="shared" si="1"/>
-        <v>3.4272441001319369E-3</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="D2:D8">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E8">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F8">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G8">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D12:D13">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E12:E13">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12:F13">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12:G13">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3474,7 +2652,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="3">
@@ -3483,7 +2661,7 @@
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="3">
@@ -3504,7 +2682,7 @@
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="3">
@@ -3525,7 +2703,7 @@
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>52</v>
       </c>
       <c r="D20" s="3">
@@ -3631,6 +2809,1207 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G17:G18">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="120.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2312764.5271400302</v>
+      </c>
+      <c r="E2" s="3">
+        <v>35420.059524999997</v>
+      </c>
+      <c r="F2" s="10">
+        <v>5.6205038026400662E-3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>1.8864917830766969E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2056038.0691327541</v>
+      </c>
+      <c r="E3" s="3">
+        <v>35306.169047820003</v>
+      </c>
+      <c r="F3" s="10">
+        <v>7.4585983781851224E-3</v>
+      </c>
+      <c r="G3" s="10">
+        <v>1.5495337612500891E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1713109.9518803279</v>
+      </c>
+      <c r="E4" s="3">
+        <v>77023.192478700003</v>
+      </c>
+      <c r="F4" s="10">
+        <v>9.4864560705148846E-3</v>
+      </c>
+      <c r="G4" s="10">
+        <v>3.0572532777723999E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1230284.2821290109</v>
+      </c>
+      <c r="E5" s="3">
+        <v>94580.340012330009</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4.1181927359240046E-3</v>
+      </c>
+      <c r="G5" s="10">
+        <v>2.9431664964802489E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1177149.00870383</v>
+      </c>
+      <c r="E6" s="3">
+        <v>54257.120220599987</v>
+      </c>
+      <c r="F6" s="10">
+        <v>3.1222927114860181E-2</v>
+      </c>
+      <c r="G6" s="10">
+        <v>4.4066793598312361E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1104497.8864203531</v>
+      </c>
+      <c r="E7" s="3">
+        <v>55926.329561999992</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1.456969533637424E-2</v>
+      </c>
+      <c r="G7" s="10">
+        <v>1.725521704280945E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1083208.9167629869</v>
+      </c>
+      <c r="E8" s="3">
+        <v>110639.49239553</v>
+      </c>
+      <c r="F8" s="10">
+        <v>6.9333248439685724E-3</v>
+      </c>
+      <c r="G8" s="10">
+        <v>1.1143475296256969E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1077864.821598877</v>
+      </c>
+      <c r="E9" s="3">
+        <v>73997.227386940009</v>
+      </c>
+      <c r="F9" s="10">
+        <v>9.7692142174449353E-3</v>
+      </c>
+      <c r="G9" s="10">
+        <v>9.558347653642385E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D10" s="3">
+        <v>729412.67096789309</v>
+      </c>
+      <c r="E10" s="3">
+        <v>60313.34351775</v>
+      </c>
+      <c r="F10" s="10">
+        <v>3.7694938920620688E-4</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1.654533485954597E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D11" s="3">
+        <v>648447.24948227091</v>
+      </c>
+      <c r="E11" s="3">
+        <v>22130.276711350001</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1.068848483528837E-2</v>
+      </c>
+      <c r="G11" s="10">
+        <v>8.5913209572516789E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D12" s="3">
+        <v>647963.01508706179</v>
+      </c>
+      <c r="E12" s="3">
+        <v>30679.58334573</v>
+      </c>
+      <c r="F12" s="10">
+        <v>6.9744795028248326E-4</v>
+      </c>
+      <c r="G12" s="10">
+        <v>1.104087647419581E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D13" s="3">
+        <v>585416.38894337451</v>
+      </c>
+      <c r="E13" s="3">
+        <v>80201.013479729998</v>
+      </c>
+      <c r="F13" s="10">
+        <v>3.0546519921711193E-4</v>
+      </c>
+      <c r="G13" s="10">
+        <v>1.7612261076438901E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="3">
+        <f>MEDIAN(D2:D13)</f>
+        <v>1093853.40159167</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="3">
+        <f>AVERAGE(D2:D7)</f>
+        <v>1598973.9542343842</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" ref="E17:G17" si="0">AVERAGE(E2:E7)</f>
+        <v>58752.201807741658</v>
+      </c>
+      <c r="F17" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2079395573083082E-2</v>
+      </c>
+      <c r="G17" s="4">
+        <f t="shared" si="0"/>
+        <v>2.5947743971152693E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="3">
+        <f>AVERAGE(D8:D13)</f>
+        <v>795385.51047374401</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" ref="E18:G18" si="1">AVERAGE(E8:E13)</f>
+        <v>62993.48947283833</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="1"/>
+        <v>4.7951477392346132E-3</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="1"/>
+        <v>2.2454820234090326E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="3">
+        <f>D17/D18</f>
+        <v>2.0103131540352179</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" ref="E20:G20" si="2">E17/E18</f>
+        <v>0.93267101567812905</v>
+      </c>
+      <c r="F20" s="3">
+        <f t="shared" si="2"/>
+        <v>2.5190872586151345</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1555534045986038</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D13">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E13">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F13">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:D18">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:E18">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:F18">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17:G18">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="93" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D2" s="3">
+        <v>9937990.5894197039</v>
+      </c>
+      <c r="E2" s="3">
+        <v>137654.50809200999</v>
+      </c>
+      <c r="F2" s="4">
+        <v>2.451646095414645E-3</v>
+      </c>
+      <c r="G2" s="4">
+        <v>7.6188786690442915E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D3" s="3">
+        <v>9153211.3096406423</v>
+      </c>
+      <c r="E3" s="3">
+        <v>158802.14720132999</v>
+      </c>
+      <c r="F3" s="4">
+        <v>2.8137256066412789E-3</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2.4032687441319662E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D4" s="3">
+        <v>8323850.3002414759</v>
+      </c>
+      <c r="E4" s="3">
+        <v>69747.682037220002</v>
+      </c>
+      <c r="F4" s="4">
+        <v>3.3950559124479012E-3</v>
+      </c>
+      <c r="G4" s="4">
+        <v>9.6936097165093425E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D5" s="3">
+        <v>7695797.0900557945</v>
+      </c>
+      <c r="E5" s="3">
+        <v>86242.724574749998</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2.8921735657111581E-3</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1.1051378185227779E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5034263.5495518269</v>
+      </c>
+      <c r="E6" s="3">
+        <v>65873.429441999993</v>
+      </c>
+      <c r="F6" s="4">
+        <v>2.9423350149191101E-3</v>
+      </c>
+      <c r="G6" s="4">
+        <v>3.4897071466789652E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D7" s="3">
+        <v>4961117.4365704898</v>
+      </c>
+      <c r="E7" s="3">
+        <v>63209.692581750001</v>
+      </c>
+      <c r="F7" s="4">
+        <v>4.351387458407175E-3</v>
+      </c>
+      <c r="G7" s="4">
+        <v>5.6592795928781631E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D8" s="3">
+        <v>4783385.1798815951</v>
+      </c>
+      <c r="E8" s="3">
+        <v>64669.840333150009</v>
+      </c>
+      <c r="F8" s="4">
+        <v>2.0954023999737231E-3</v>
+      </c>
+      <c r="G8" s="4">
+        <v>5.9056880507593645E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D9" s="3">
+        <v>4448196.0441567702</v>
+      </c>
+      <c r="E9" s="3">
+        <v>96473.926682400008</v>
+      </c>
+      <c r="F9" s="4">
+        <v>4.425446074207404E-4</v>
+      </c>
+      <c r="G9" s="4">
+        <v>2.154034060250509E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1252686.154182706</v>
+      </c>
+      <c r="E10" s="3">
+        <v>9796.3168782600005</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.13430184443805829</v>
+      </c>
+      <c r="G10" s="4">
+        <v>5.218380319387952E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1194490.274669243</v>
+      </c>
+      <c r="E11" s="3">
+        <v>19231.118310289999</v>
+      </c>
+      <c r="F11" s="4">
+        <v>5.2147019888250969E-3</v>
+      </c>
+      <c r="G11" s="4">
+        <v>4.9058279907476332E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1165717.934645507</v>
+      </c>
+      <c r="E12" s="3">
+        <v>8785.8682089999984</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1.025148686019859E-2</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1.7444704536200269E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1063712.5319653209</v>
+      </c>
+      <c r="E13" s="3">
+        <v>8180.2586681400007</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1.6866644248961379E-2</v>
+      </c>
+      <c r="G13" s="4">
+        <v>6.3103132179727491E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="3">
+        <f>MEDIAN(D2:D13)</f>
+        <v>4872251.3082260424</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="6"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="3">
+        <f>AVERAGE(D2:D7)</f>
+        <v>7517705.0459133228</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" ref="E17:G17" si="0">AVERAGE(E2:E7)</f>
+        <v>96921.697321510001</v>
+      </c>
+      <c r="F17" s="4">
+        <f t="shared" si="0"/>
+        <v>3.141053942256878E-3</v>
+      </c>
+      <c r="G17" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0257590125276369E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="3">
+        <f>AVERAGE(D8:D13)</f>
+        <v>2318031.3532501906</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" ref="E18:G18" si="1">AVERAGE(E8:E13)</f>
+        <v>34522.888180206675</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="1"/>
+        <v>2.8195437423906299E-2</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="1"/>
+        <v>4.3731190154563726E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D23" s="3">
+        <v>5034263.5495518269</v>
+      </c>
+      <c r="E23" s="3">
+        <v>65873.429441999993</v>
+      </c>
+      <c r="F23" s="4">
+        <v>2.9423350149191101E-3</v>
+      </c>
+      <c r="G23" s="4">
+        <v>3.4897071466789652E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D24" s="3">
+        <v>4961117.4365704898</v>
+      </c>
+      <c r="E24" s="3">
+        <v>63209.692581750001</v>
+      </c>
+      <c r="F24" s="4">
+        <v>4.351387458407175E-3</v>
+      </c>
+      <c r="G24" s="4">
+        <v>5.6592795928781631E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D25" s="3">
+        <v>4783385.1798815951</v>
+      </c>
+      <c r="E25" s="3">
+        <v>64669.840333150009</v>
+      </c>
+      <c r="F25" s="4">
+        <v>2.0954023999737231E-3</v>
+      </c>
+      <c r="G25" s="4">
+        <v>5.9056880507593645E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D26" s="3">
+        <v>4448196.0441567702</v>
+      </c>
+      <c r="E26" s="3">
+        <v>96473.926682400008</v>
+      </c>
+      <c r="F26" s="4">
+        <v>4.425446074207404E-4</v>
+      </c>
+      <c r="G26" s="4">
+        <v>2.154034060250509E-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="3">
+        <f>AVERAGE(D23:D24)</f>
+        <v>4997690.4930611588</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" ref="E28:G28" si="2">AVERAGE(E23:E24)</f>
+        <v>64541.561011874997</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="2"/>
+        <v>3.6468612366631426E-3</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="2"/>
+        <v>4.5744933697785639E-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="3">
+        <f>AVERAGE(D25:D26)</f>
+        <v>4615790.6120191831</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" ref="E29:G29" si="3">AVERAGE(E25:E26)</f>
+        <v>80571.883507775012</v>
+      </c>
+      <c r="F29" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2689735036972318E-3</v>
+      </c>
+      <c r="G29" s="4">
+        <f t="shared" si="3"/>
+        <v>4.0298610555049367E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="3">
+        <f>D28/D29</f>
+        <v>1.0827376961267559</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" ref="E31:G31" si="4">E28/E29</f>
+        <v>0.80104322006630113</v>
+      </c>
+      <c r="F31" s="3">
+        <f t="shared" si="4"/>
+        <v>2.8738671264906555</v>
+      </c>
+      <c r="G31" s="3">
+        <f t="shared" si="4"/>
+        <v>1.1351491544676557</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D13">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E13">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F13">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:D18">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:E18">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:F18">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17:G18">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D23:D26">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E23:E26">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23:F26">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G23:G26">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D28:D29">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E28:E29">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28:F29">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28:G29">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -3647,6 +4026,1205 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="97.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D2" s="3">
+        <v>3292837.3871137551</v>
+      </c>
+      <c r="E2" s="3">
+        <v>5258.5701260400001</v>
+      </c>
+      <c r="F2" s="4">
+        <v>1.0604360748915839E-2</v>
+      </c>
+      <c r="G2" s="4">
+        <v>1.868819729404374E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3097084.3107878752</v>
+      </c>
+      <c r="E3" s="3">
+        <v>4162.4721680000002</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1.4081114307645259E-3</v>
+      </c>
+      <c r="G3" s="4">
+        <v>3.9573959548935052E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2652658.7944572391</v>
+      </c>
+      <c r="E4" s="3">
+        <v>4253.6615775199998</v>
+      </c>
+      <c r="F4" s="4">
+        <v>2.8806641846538372E-3</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1.8380008135386839E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2480166.278394436</v>
+      </c>
+      <c r="E5" s="3">
+        <v>4510.0316159999993</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1.003512255644462E-3</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1.2206708220113729E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D6" s="3">
+        <v>331647.0310656284</v>
+      </c>
+      <c r="E6" s="3">
+        <v>964.84556195999994</v>
+      </c>
+      <c r="F6" s="4">
+        <v>7.4163848413873461E-4</v>
+      </c>
+      <c r="G6" s="4">
+        <v>3.6380912535570372E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D7" s="3">
+        <v>255261.79722573471</v>
+      </c>
+      <c r="E7" s="3">
+        <v>888.20773440000005</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1.2066660967819649E-3</v>
+      </c>
+      <c r="G7" s="4">
+        <v>2.863735386990569E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D8" s="3">
+        <v>238996.75153477999</v>
+      </c>
+      <c r="E8" s="3">
+        <v>863.40619829999991</v>
+      </c>
+      <c r="F8" s="4">
+        <v>7.0023981897559661E-4</v>
+      </c>
+      <c r="G8" s="4">
+        <v>9.1753228267274999E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D9" s="3">
+        <v>218314.63160777459</v>
+      </c>
+      <c r="E9" s="3">
+        <v>897.65553599999998</v>
+      </c>
+      <c r="F9" s="4">
+        <v>4.6312642581418888E-4</v>
+      </c>
+      <c r="G9" s="4">
+        <v>5.3328786021100191E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D10" s="3">
+        <v>177476.11420904889</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1454.99992092</v>
+      </c>
+      <c r="F10" s="4">
+        <v>2.7347370558508639E-4</v>
+      </c>
+      <c r="G10" s="4">
+        <v>8.7625687236728058E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D11" s="3">
+        <v>149725.9222474432</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1319.2765561000001</v>
+      </c>
+      <c r="F11" s="4">
+        <v>9.5143491498901212E-3</v>
+      </c>
+      <c r="G11" s="4">
+        <v>8.6555389370039323E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D12" s="3">
+        <v>123407.0292947656</v>
+      </c>
+      <c r="E12" s="3">
+        <v>769.72569599999997</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1.643806367093142E-3</v>
+      </c>
+      <c r="G12" s="4">
+        <v>4.963035559098705E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D13" s="3">
+        <v>118648.02708896549</v>
+      </c>
+      <c r="E13" s="3">
+        <v>640.62859736000007</v>
+      </c>
+      <c r="F13" s="4">
+        <v>4.2703506076277667E-2</v>
+      </c>
+      <c r="G13" s="4">
+        <v>7.645975624855611E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="3">
+        <f>MEDIAN(D2:D13)</f>
+        <v>247129.27438025735</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="6"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="3">
+        <f>AVERAGE(D2:D7)</f>
+        <v>2018275.9331741116</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" ref="E17:G17" si="0">AVERAGE(E2:E7)</f>
+        <v>3339.6314639866664</v>
+      </c>
+      <c r="F17" s="4">
+        <f t="shared" si="0"/>
+        <v>2.974158866816561E-3</v>
+      </c>
+      <c r="G17" s="4">
+        <f t="shared" si="0"/>
+        <v>2.0187386386990346E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="3">
+        <f>AVERAGE(D8:D13)</f>
+        <v>171094.74599712962</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" ref="E18:G18" si="1">AVERAGE(E8:E13)</f>
+        <v>990.94875077999995</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="1"/>
+        <v>9.2164169239392999E-3</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="1"/>
+        <v>3.4335388058007936E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="3">
+        <f>D17/D18</f>
+        <v>11.796247286330882</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" ref="E20:G20" si="2">E17/E18</f>
+        <v>3.3701353993917049</v>
+      </c>
+      <c r="F20" s="3">
+        <f t="shared" si="2"/>
+        <v>0.32270229215556578</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="2"/>
+        <v>0.58794694129813696</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D24" s="3">
+        <v>3292837.3871137551</v>
+      </c>
+      <c r="E24" s="3">
+        <v>5258.5701260400001</v>
+      </c>
+      <c r="F24" s="4">
+        <v>1.0604360748915839E-2</v>
+      </c>
+      <c r="G24" s="4">
+        <v>1.868819729404374E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D25" s="3">
+        <v>3097084.3107878752</v>
+      </c>
+      <c r="E25" s="3">
+        <v>4162.4721680000002</v>
+      </c>
+      <c r="F25" s="4">
+        <v>1.4081114307645259E-3</v>
+      </c>
+      <c r="G25" s="4">
+        <v>3.9573959548935052E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D26" s="3">
+        <v>2652658.7944572391</v>
+      </c>
+      <c r="E26" s="3">
+        <v>4253.6615775199998</v>
+      </c>
+      <c r="F26" s="4">
+        <v>2.8806641846538372E-3</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1.8380008135386839E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D27" s="3">
+        <v>2480166.278394436</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4510.0316159999993</v>
+      </c>
+      <c r="F27" s="4">
+        <v>1.003512255644462E-3</v>
+      </c>
+      <c r="G27" s="4">
+        <v>1.2206708220113729E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="3">
+        <f>AVERAGE(D24:D25)</f>
+        <v>3194960.8489508154</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" ref="E29:G30" si="3">AVERAGE(E24:E25)</f>
+        <v>4710.5211470200002</v>
+      </c>
+      <c r="F29" s="4">
+        <f t="shared" si="3"/>
+        <v>6.0062360898401829E-3</v>
+      </c>
+      <c r="G29" s="4">
+        <f t="shared" si="3"/>
+        <v>2.9131078421489398E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="3">
+        <f>AVERAGE(D26:D27)</f>
+        <v>2566412.5364258373</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" ref="E30:G30" si="4">AVERAGE(E26:E27)</f>
+        <v>4381.8465967599996</v>
+      </c>
+      <c r="F30" s="4">
+        <f t="shared" si="4"/>
+        <v>1.9420882201491496E-3</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" si="4"/>
+        <v>1.5293358177750284E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="3">
+        <f>D29/D30</f>
+        <v>1.2449132022244318</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" ref="E32:G32" si="5">E29/E30</f>
+        <v>1.0750082283809359</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" si="5"/>
+        <v>3.092669028896593</v>
+      </c>
+      <c r="G32" s="3">
+        <f t="shared" si="5"/>
+        <v>1.9048189470819483</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:G13">
+    <sortCondition descending="1" ref="D2:D13"/>
+  </sortState>
+  <conditionalFormatting sqref="D2:D13">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E13">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F13">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:D18">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:E18">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:F18">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17:G18">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D24:D27">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E24:E27">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24:F27">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24:G27">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:D30">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29:E30">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29:F30">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29:G30">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="73" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D2" s="3">
+        <v>971947.1589226143</v>
+      </c>
+      <c r="E2" s="3">
+        <v>21731.663739110001</v>
+      </c>
+      <c r="F2" s="4">
+        <v>3.0282081846115981E-5</v>
+      </c>
+      <c r="G2" s="4">
+        <v>5.0206173563068553E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D3" s="3">
+        <v>950234.48563991196</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3253.0570836699999</v>
+      </c>
+      <c r="F3" s="4">
+        <v>3.2666995157709352E-4</v>
+      </c>
+      <c r="G3" s="4">
+        <v>1.167450820049999E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D4" s="3">
+        <v>840420.70663642394</v>
+      </c>
+      <c r="E4" s="3">
+        <v>22097.462448999999</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1.047846559460851E-5</v>
+      </c>
+      <c r="G4" s="4">
+        <v>8.9257472528899238E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D5" s="3">
+        <v>130071.2900498806</v>
+      </c>
+      <c r="E5" s="3">
+        <v>866.32844524999996</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1.8830176464184379E-3</v>
+      </c>
+      <c r="G5" s="4">
+        <v>2.5735129813919731E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D6" s="3">
+        <v>118956.3612196709</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1090.8420791399999</v>
+      </c>
+      <c r="F6" s="4">
+        <v>6.857037460360029E-4</v>
+      </c>
+      <c r="G6" s="4">
+        <v>4.8025762850386331E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D7" s="3">
+        <v>106346.7598437235</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1736.36278023</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2.7534118528886658E-3</v>
+      </c>
+      <c r="G7" s="4">
+        <v>9.5257384161442811E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D8" s="3">
+        <v>85809.083743767143</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2740.6294030899999</v>
+      </c>
+      <c r="F8" s="4">
+        <v>3.444045779906578E-2</v>
+      </c>
+      <c r="G8" s="4">
+        <v>2.7573625574766692E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="3">
+        <f>MEDIAN(D2:D8)</f>
+        <v>130071.2900498806</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="6"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="3">
+        <f>AVERAGE(D2:D4)</f>
+        <v>920867.45039964991</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" ref="E12:G12" si="0">AVERAGE(E2:E4)</f>
+        <v>15694.061090593334</v>
+      </c>
+      <c r="F12" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2247683300593934E-4</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="0"/>
+        <v>5.0379384764155924E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="3">
+        <f>AVERAGE(D6:D8)</f>
+        <v>103704.06826905387</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" ref="E13:G13" si="1">AVERAGE(E6:E8)</f>
+        <v>1855.9447541533334</v>
+      </c>
+      <c r="F13" s="4">
+        <f t="shared" si="1"/>
+        <v>1.2626524465996816E-2</v>
+      </c>
+      <c r="G13" s="4">
+        <f t="shared" si="1"/>
+        <v>3.4272441001319369E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="3">
+        <f>D12/D13</f>
+        <v>8.8797620553372667</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" ref="E15:G15" si="2">E12/E13</f>
+        <v>8.4561035857734002</v>
+      </c>
+      <c r="F15" s="3">
+        <f t="shared" si="2"/>
+        <v>9.6999640190591641E-3</v>
+      </c>
+      <c r="G15" s="3">
+        <f t="shared" si="2"/>
+        <v>1.469967801891219</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D8">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E8">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F8">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G8">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D12:D13">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E12:E13">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12:F13">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G13">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19:D22">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19:E22">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19:F22">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19:G22">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3681,10 +5259,10 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3710,10 +5288,10 @@
       <c r="G2" s="4">
         <v>9.1204876912707078E-4</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="8" t="s">
         <v>67</v>
       </c>
     </row>
@@ -3739,10 +5317,10 @@
       <c r="G3" s="4">
         <v>1.009990774998547E-3</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3791,7 +5369,7 @@
       <c r="G5" s="4">
         <v>6.8807976565944413E-4</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4075,7 +5653,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D19">
@@ -4084,10 +5662,10 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C20" s="7"/>
+      <c r="C20" s="6"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C21" s="7"/>
+      <c r="C21" s="6"/>
       <c r="D21" s="1" t="s">
         <v>63</v>
       </c>
@@ -4102,7 +5680,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>79</v>
       </c>
       <c r="D22" s="2">
@@ -4123,7 +5701,7 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>80</v>
       </c>
       <c r="D23" s="2">
@@ -4193,7 +5771,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D23">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4205,7 +5783,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22:E23">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4217,7 +5795,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:F23">
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4229,7 +5807,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G22:G23">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4243,951 +5821,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="93" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D2" s="3">
-        <v>9937990.5894197039</v>
-      </c>
-      <c r="E2" s="3">
-        <v>137654.50809200999</v>
-      </c>
-      <c r="F2" s="4">
-        <v>2.451646095414645E-3</v>
-      </c>
-      <c r="G2" s="4">
-        <v>7.6188786690442915E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D3" s="3">
-        <v>9153211.3096406423</v>
-      </c>
-      <c r="E3" s="3">
-        <v>158802.14720132999</v>
-      </c>
-      <c r="F3" s="4">
-        <v>2.8137256066412789E-3</v>
-      </c>
-      <c r="G3" s="4">
-        <v>2.4032687441319662E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D4" s="3">
-        <v>8323850.3002414759</v>
-      </c>
-      <c r="E4" s="3">
-        <v>69747.682037220002</v>
-      </c>
-      <c r="F4" s="4">
-        <v>3.3950559124479012E-3</v>
-      </c>
-      <c r="G4" s="4">
-        <v>9.6936097165093425E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D5" s="3">
-        <v>7695797.0900557945</v>
-      </c>
-      <c r="E5" s="3">
-        <v>86242.724574749998</v>
-      </c>
-      <c r="F5" s="4">
-        <v>2.8921735657111581E-3</v>
-      </c>
-      <c r="G5" s="4">
-        <v>1.1051378185227779E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D6" s="3">
-        <v>5034263.5495518269</v>
-      </c>
-      <c r="E6" s="3">
-        <v>65873.429441999993</v>
-      </c>
-      <c r="F6" s="4">
-        <v>2.9423350149191101E-3</v>
-      </c>
-      <c r="G6" s="4">
-        <v>3.4897071466789652E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D7" s="3">
-        <v>4961117.4365704898</v>
-      </c>
-      <c r="E7" s="3">
-        <v>63209.692581750001</v>
-      </c>
-      <c r="F7" s="4">
-        <v>4.351387458407175E-3</v>
-      </c>
-      <c r="G7" s="4">
-        <v>5.6592795928781631E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D8" s="3">
-        <v>4783385.1798815951</v>
-      </c>
-      <c r="E8" s="3">
-        <v>64669.840333150009</v>
-      </c>
-      <c r="F8" s="4">
-        <v>2.0954023999737231E-3</v>
-      </c>
-      <c r="G8" s="4">
-        <v>5.9056880507593645E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D9" s="3">
-        <v>4448196.0441567702</v>
-      </c>
-      <c r="E9" s="3">
-        <v>96473.926682400008</v>
-      </c>
-      <c r="F9" s="4">
-        <v>4.425446074207404E-4</v>
-      </c>
-      <c r="G9" s="4">
-        <v>2.154034060250509E-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D10" s="3">
-        <v>1252686.154182706</v>
-      </c>
-      <c r="E10" s="3">
-        <v>9796.3168782600005</v>
-      </c>
-      <c r="F10" s="4">
-        <v>0.13430184443805829</v>
-      </c>
-      <c r="G10" s="4">
-        <v>5.218380319387952E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D11" s="3">
-        <v>1194490.274669243</v>
-      </c>
-      <c r="E11" s="3">
-        <v>19231.118310289999</v>
-      </c>
-      <c r="F11" s="4">
-        <v>5.2147019888250969E-3</v>
-      </c>
-      <c r="G11" s="4">
-        <v>4.9058279907476332E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1165717.934645507</v>
-      </c>
-      <c r="E12" s="3">
-        <v>8785.8682089999984</v>
-      </c>
-      <c r="F12" s="4">
-        <v>1.025148686019859E-2</v>
-      </c>
-      <c r="G12" s="4">
-        <v>1.7444704536200269E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D13" s="3">
-        <v>1063712.5319653209</v>
-      </c>
-      <c r="E13" s="3">
-        <v>8180.2586681400007</v>
-      </c>
-      <c r="F13" s="4">
-        <v>1.6866644248961379E-2</v>
-      </c>
-      <c r="G13" s="4">
-        <v>6.3103132179727491E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="3">
-        <f>MEDIAN(D2:D13)</f>
-        <v>4872251.3082260424</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="3">
-        <f>AVERAGE(D2:D7)</f>
-        <v>7517705.0459133228</v>
-      </c>
-      <c r="E17" s="3">
-        <f t="shared" ref="E17:G17" si="0">AVERAGE(E2:E7)</f>
-        <v>96921.697321510001</v>
-      </c>
-      <c r="F17" s="4">
-        <f t="shared" si="0"/>
-        <v>3.141053942256878E-3</v>
-      </c>
-      <c r="G17" s="4">
-        <f t="shared" si="0"/>
-        <v>1.0257590125276369E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="3">
-        <f>AVERAGE(D8:D13)</f>
-        <v>2318031.3532501906</v>
-      </c>
-      <c r="E18" s="3">
-        <f t="shared" ref="E18:G18" si="1">AVERAGE(E8:E13)</f>
-        <v>34522.888180206675</v>
-      </c>
-      <c r="F18" s="4">
-        <f t="shared" si="1"/>
-        <v>2.8195437423906299E-2</v>
-      </c>
-      <c r="G18" s="4">
-        <f t="shared" si="1"/>
-        <v>4.3731190154563726E-4</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="D2:D13">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D17:D18">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E17:E18">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17:F18">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="120.28515625" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D2" s="3">
-        <v>2312764.5271400302</v>
-      </c>
-      <c r="E2" s="3">
-        <v>35420.059524999997</v>
-      </c>
-      <c r="F2" s="11">
-        <v>5.6205038026400662E-3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>1.8864917830766969E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D3" s="3">
-        <v>2056038.0691327541</v>
-      </c>
-      <c r="E3" s="3">
-        <v>35306.169047820003</v>
-      </c>
-      <c r="F3" s="11">
-        <v>7.4585983781851224E-3</v>
-      </c>
-      <c r="G3" s="11">
-        <v>1.5495337612500891E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1713109.9518803279</v>
-      </c>
-      <c r="E4" s="3">
-        <v>77023.192478700003</v>
-      </c>
-      <c r="F4" s="11">
-        <v>9.4864560705148846E-3</v>
-      </c>
-      <c r="G4" s="11">
-        <v>3.0572532777723999E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1230284.2821290109</v>
-      </c>
-      <c r="E5" s="3">
-        <v>94580.340012330009</v>
-      </c>
-      <c r="F5" s="11">
-        <v>4.1181927359240046E-3</v>
-      </c>
-      <c r="G5" s="11">
-        <v>2.9431664964802489E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1177149.00870383</v>
-      </c>
-      <c r="E6" s="3">
-        <v>54257.120220599987</v>
-      </c>
-      <c r="F6" s="11">
-        <v>3.1222927114860181E-2</v>
-      </c>
-      <c r="G6" s="11">
-        <v>4.4066793598312361E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1104497.8864203531</v>
-      </c>
-      <c r="E7" s="3">
-        <v>55926.329561999992</v>
-      </c>
-      <c r="F7" s="11">
-        <v>1.456969533637424E-2</v>
-      </c>
-      <c r="G7" s="11">
-        <v>1.725521704280945E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1083208.9167629869</v>
-      </c>
-      <c r="E8" s="3">
-        <v>110639.49239553</v>
-      </c>
-      <c r="F8" s="11">
-        <v>6.9333248439685724E-3</v>
-      </c>
-      <c r="G8" s="11">
-        <v>1.1143475296256969E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1077864.821598877</v>
-      </c>
-      <c r="E9" s="3">
-        <v>73997.227386940009</v>
-      </c>
-      <c r="F9" s="11">
-        <v>9.7692142174449353E-3</v>
-      </c>
-      <c r="G9" s="11">
-        <v>9.558347653642385E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D10" s="3">
-        <v>729412.67096789309</v>
-      </c>
-      <c r="E10" s="3">
-        <v>60313.34351775</v>
-      </c>
-      <c r="F10" s="11">
-        <v>3.7694938920620688E-4</v>
-      </c>
-      <c r="G10" s="11">
-        <v>1.654533485954597E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D11" s="3">
-        <v>648447.24948227091</v>
-      </c>
-      <c r="E11" s="3">
-        <v>22130.276711350001</v>
-      </c>
-      <c r="F11" s="11">
-        <v>1.068848483528837E-2</v>
-      </c>
-      <c r="G11" s="11">
-        <v>8.5913209572516789E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D12" s="3">
-        <v>647963.01508706179</v>
-      </c>
-      <c r="E12" s="3">
-        <v>30679.58334573</v>
-      </c>
-      <c r="F12" s="11">
-        <v>6.9744795028248326E-4</v>
-      </c>
-      <c r="G12" s="11">
-        <v>1.104087647419581E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C13" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D13" s="3">
-        <v>585416.38894337451</v>
-      </c>
-      <c r="E13" s="3">
-        <v>80201.013479729998</v>
-      </c>
-      <c r="F13" s="11">
-        <v>3.0546519921711193E-4</v>
-      </c>
-      <c r="G13" s="11">
-        <v>1.7612261076438901E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="3">
-        <f>MEDIAN(D2:D13)</f>
-        <v>1093853.40159167</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="3">
-        <f>AVERAGE(D2:D7)</f>
-        <v>1598973.9542343842</v>
-      </c>
-      <c r="E17" s="3">
-        <f t="shared" ref="E17:G17" si="0">AVERAGE(E2:E7)</f>
-        <v>58752.201807741658</v>
-      </c>
-      <c r="F17" s="4">
-        <f t="shared" si="0"/>
-        <v>1.2079395573083082E-2</v>
-      </c>
-      <c r="G17" s="4">
-        <f t="shared" si="0"/>
-        <v>2.5947743971152693E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="3">
-        <f>AVERAGE(D8:D13)</f>
-        <v>795385.51047374401</v>
-      </c>
-      <c r="E18" s="3">
-        <f t="shared" ref="E18:G18" si="1">AVERAGE(E8:E13)</f>
-        <v>62993.48947283833</v>
-      </c>
-      <c r="F18" s="4">
-        <f t="shared" si="1"/>
-        <v>4.7951477392346132E-3</v>
-      </c>
-      <c r="G18" s="4">
-        <f t="shared" si="1"/>
-        <v>2.2454820234090326E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="3">
-        <f>D17/D18</f>
-        <v>2.0103131540352179</v>
-      </c>
-      <c r="E20" s="3">
-        <f t="shared" ref="E20:G20" si="2">E17/E18</f>
-        <v>0.93267101567812905</v>
-      </c>
-      <c r="F20" s="3">
-        <f t="shared" si="2"/>
-        <v>2.5190872586151345</v>
-      </c>
-      <c r="G20" s="3">
-        <f t="shared" si="2"/>
-        <v>1.1555534045986038</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="D2:D13">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D17:D18">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E17:E18">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17:F18">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/clustering/sepsectors/sector analysis (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/sector analysis (VDS_s) 0.xlsx
@@ -15,17 +15,18 @@
     <sheet name="Пром. производство" sheetId="3" r:id="rId1"/>
     <sheet name="Логистика" sheetId="4" r:id="rId2"/>
     <sheet name="Наука" sheetId="7" r:id="rId3"/>
-    <sheet name="Торговля" sheetId="6" r:id="rId4"/>
-    <sheet name="Сельхоз" sheetId="1" r:id="rId5"/>
-    <sheet name="Административный" sheetId="2" r:id="rId6"/>
-    <sheet name="Добыча" sheetId="5" r:id="rId7"/>
+    <sheet name="Строительство" sheetId="8" r:id="rId4"/>
+    <sheet name="Торговля" sheetId="6" r:id="rId5"/>
+    <sheet name="Сельхоз" sheetId="1" r:id="rId6"/>
+    <sheet name="Административный" sheetId="2" r:id="rId7"/>
+    <sheet name="Добыча" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="99">
   <si>
     <t>sector</t>
   </si>
@@ -304,6 +305,24 @@
   </si>
   <si>
     <t>73</t>
+  </si>
+  <si>
+    <t>Строительство зданий</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Строительство инженерных сооружений</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Работы строительные специализированные</t>
+  </si>
+  <si>
+    <t>43</t>
   </si>
 </sst>
 </file>
@@ -313,7 +332,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,6 +370,11 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -395,7 +419,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -422,6 +446,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3310,6 +3337,401 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D2" s="3">
+        <v>3162049.709016114</v>
+      </c>
+      <c r="E2" s="3">
+        <v>28754.301122820001</v>
+      </c>
+      <c r="F2" s="4">
+        <v>4.4816202664626553E-3</v>
+      </c>
+      <c r="G2" s="4">
+        <v>8.4653638062801126E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3063178.2048380482</v>
+      </c>
+      <c r="E3" s="3">
+        <v>4552.0415732800002</v>
+      </c>
+      <c r="F3" s="4">
+        <v>5.8592278586730327E-3</v>
+      </c>
+      <c r="G3" s="4">
+        <v>6.9752471915851143E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2844592.645754816</v>
+      </c>
+      <c r="E4" s="3">
+        <v>13495.267380560001</v>
+      </c>
+      <c r="F4" s="4">
+        <v>9.4137314672996359E-4</v>
+      </c>
+      <c r="G4" s="4">
+        <v>4.9632040263599883E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1986156.080578048</v>
+      </c>
+      <c r="E5" s="3">
+        <v>10023.30762064</v>
+      </c>
+      <c r="F5" s="4">
+        <v>8.3094423869115915E-3</v>
+      </c>
+      <c r="G5" s="4">
+        <v>2.6112463660302979E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1956784.5814760141</v>
+      </c>
+      <c r="E6" s="3">
+        <v>13840.213139900001</v>
+      </c>
+      <c r="F6" s="4">
+        <v>5.5526598631959554E-4</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1.7115461706084071E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1934582.820337062</v>
+      </c>
+      <c r="E7" s="3">
+        <v>4804.5085313400004</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1.828511270756302E-3</v>
+      </c>
+      <c r="G7" s="4">
+        <v>2.0188332181595189E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1929006.46472436</v>
+      </c>
+      <c r="E8" s="3">
+        <v>30751.247821140001</v>
+      </c>
+      <c r="F8" s="4">
+        <v>3.6624865779454649E-4</v>
+      </c>
+      <c r="G8" s="4">
+        <v>3.3220418369420449E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1847753.5707314</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3004.4345673600001</v>
+      </c>
+      <c r="F9" s="4">
+        <v>4.726564124336423E-3</v>
+      </c>
+      <c r="G9" s="4">
+        <v>4.5218654277226359E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1771136.789893996</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2860.9363756799999</v>
+      </c>
+      <c r="F10" s="4">
+        <v>2.9910971431393869E-3</v>
+      </c>
+      <c r="G10" s="4">
+        <v>5.8399632169480961E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="3">
+        <f>MEDIAN(D2:D10)</f>
+        <v>1956784.5814760141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="3">
+        <f>AVERAGE(D2:D5)</f>
+        <v>2763994.1600467563</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" ref="E14:G14" si="0">AVERAGE(E2:E5)</f>
+        <v>14206.229424325</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" si="0"/>
+        <v>4.8979159146943108E-3</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="0"/>
+        <v>5.7537653475638788E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="3">
+        <f>AVERAGE(D7:D10)</f>
+        <v>1870619.9114217046</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" ref="E15:G15" si="1">AVERAGE(E7:E10)</f>
+        <v>10355.281823879999</v>
+      </c>
+      <c r="F15" s="4">
+        <f t="shared" si="1"/>
+        <v>2.4781052990066645E-3</v>
+      </c>
+      <c r="G15" s="4">
+        <f t="shared" si="1"/>
+        <v>8.468050665801991E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D10">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E10">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F10">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G10">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14:D15">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14:E15">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:F15">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G14:G15">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4025,7 +4447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4512,7 +4934,7 @@
         <v>3194960.8489508154</v>
       </c>
       <c r="E29" s="3">
-        <f t="shared" ref="E29:G30" si="3">AVERAGE(E24:E25)</f>
+        <f t="shared" ref="E29:G29" si="3">AVERAGE(E24:E25)</f>
         <v>4710.5211470200002</v>
       </c>
       <c r="F29" s="4">
@@ -4767,7 +5189,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5224,7 +5646,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/clustering/sepsectors/sector analysis (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/sector analysis (VDS_s) 0.xlsx
@@ -9,24 +9,25 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
   </bookViews>
   <sheets>
-    <sheet name="Пром. производство" sheetId="3" r:id="rId1"/>
-    <sheet name="Логистика" sheetId="4" r:id="rId2"/>
-    <sheet name="Наука" sheetId="7" r:id="rId3"/>
-    <sheet name="Строительство" sheetId="8" r:id="rId4"/>
-    <sheet name="Торговля" sheetId="6" r:id="rId5"/>
-    <sheet name="Сельхоз" sheetId="1" r:id="rId6"/>
-    <sheet name="Административный" sheetId="2" r:id="rId7"/>
-    <sheet name="Добыча" sheetId="5" r:id="rId8"/>
+    <sheet name="Внутрисекторальная разница" sheetId="9" r:id="rId1"/>
+    <sheet name="Пром. производство" sheetId="3" r:id="rId2"/>
+    <sheet name="Логистика" sheetId="4" r:id="rId3"/>
+    <sheet name="Наука" sheetId="7" r:id="rId4"/>
+    <sheet name="Строительство" sheetId="8" r:id="rId5"/>
+    <sheet name="Торговля" sheetId="6" r:id="rId6"/>
+    <sheet name="Сельхоз" sheetId="1" r:id="rId7"/>
+    <sheet name="Административный" sheetId="2" r:id="rId8"/>
+    <sheet name="Добыча" sheetId="5" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="99">
   <si>
     <t>sector</t>
   </si>
@@ -419,7 +420,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -449,6 +450,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -753,6 +758,830 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F58"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="107.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1.1520246843183004</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2.3213939799145842</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0.80614296667612206</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.25898323939199175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1.3517669960910756</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1.9670776981935643</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.22070836576565364</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.13814015553291181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1.1917367114224651</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1.9004800470248358</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.8374708956221617</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1.5257452190518532</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1.0878384484836321</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1.7638605592859029</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.17960036588529976</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.1305356718336195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1.0976688735092679</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1.7109052289159346</v>
+      </c>
+      <c r="E6" s="3">
+        <v>5.1447699646144658</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1.2569187110314528</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1.3902001109844437</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1.462361279754929</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.71207716480109773</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1.2647790839496653</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1.1404823836685474</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1.2854689383527957</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.8632074718882139</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2.5147412702861627</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1.0516922481844897</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1.2423192338416251</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.40890802664562625</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1.7538454461835107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1.2659566944389276</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1.1816122280015293</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4.0293347314057506</v>
+      </c>
+      <c r="F10" s="3">
+        <v>12.618953438776055</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1.2868516961482879</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1.1177412074865631</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.10176095000792922</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1.2821795576565411</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1.2800215472650383</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.090543283688677</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1.3904082000767517</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.297125195307224</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1.2449132022244318</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1.0750082283809359</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3.092669028896593</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1.9048189470819483</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1.2833899393849333</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1.0522364209432813</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1.6747130060256721</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.51637317479464306</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1.4503287429709963</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1.0419486207404769</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.6663471741165341</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1.2983469738919464</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1.1026252311808127</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.99574889178403025</v>
+      </c>
+      <c r="E16" s="3">
+        <v>44.739847820807242</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.8055055175801521</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1.0547425539337831</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.9009903074402914</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.59798991148430225</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3.0757485240645135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1.2859286844144691</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.88933632105715787</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1.3200782438717298</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.63162779932699387</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1.0515020276116822</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.88110216515673767</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1.5793790877321685</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1.5532186573951297</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1.1718069796331221</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0.82231497292558131</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1.0066845075285169</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0.95392645329154935</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1.0827376961267559</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0.80104322006630113</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2.8738671264906555</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1.1351491544676557</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1.0607758459664012</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0.77167677289668257</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0.82036156049346076</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1.4287748577228767</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1.1171419888702492</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0.74353514130949905</v>
+      </c>
+      <c r="E23" s="3">
+        <v>11.033292593696363</v>
+      </c>
+      <c r="F23" s="3">
+        <v>8.7727411256017351</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1.1452682356283854</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0.71970300745850779</v>
+      </c>
+      <c r="E24" s="3">
+        <v>6.5995587829731441</v>
+      </c>
+      <c r="F24" s="3">
+        <v>4.1985328533946333</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1.0557931710621387</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0.59675805501967727</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2.741656360321008</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0.57456911856021375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1.3306477779394272</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0.52497104851926879</v>
+      </c>
+      <c r="E26" s="3">
+        <v>14.558529260558757</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0.20311492992969613</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="3">
+        <v>1.116815947298657</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0.51990063688275234</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2.5220307584192545</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0.22602584912178772</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1.2959670995181913</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0.43716192574154161</v>
+      </c>
+      <c r="E28" s="3">
+        <v>6.9063031528892316E-2</v>
+      </c>
+      <c r="F28" s="3">
+        <v>7.525489289467116E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="3">
+        <v>1.4842736816541999</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0.4121490248256805</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0.96137007040086431</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0.57263086143914699</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1.2626658353400688</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0.23138177613322164</v>
+      </c>
+      <c r="E30" s="3">
+        <v>15.780848016319494</v>
+      </c>
+      <c r="F30" s="3">
+        <v>0.9262386419932308</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B31" s="12"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="12"/>
+      <c r="C32" s="3">
+        <f>AVERAGE(C2:C16)</f>
+        <v>1.2251665006850432</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="12"/>
+      <c r="C33" s="3">
+        <f>AVERAGE(C17:C30)</f>
+        <v>1.1797191089283952</v>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="12"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B35" s="12"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B36" s="12"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="12"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="12"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" s="12"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40" s="12"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B41" s="12"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B42" s="12"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B43" s="12"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B44" s="12"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B45" s="12"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B46" s="12"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="12"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="12"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B49" s="12"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B50" s="12"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B51" s="12"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B52" s="12"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B53" s="12"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B54" s="12"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B55" s="12"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B56" s="12"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B57" s="12"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+    </row>
+  </sheetData>
+  <sortState ref="A2:F30">
+    <sortCondition descending="1" ref="D2:D30"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2367,7 +3196,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2851,7 +3680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3335,7 +4164,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3730,7 +4559,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4447,7 +5276,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5189,7 +6018,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5646,9 +6475,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="67" customWidth="1"/>
@@ -6143,8 +6972,515 @@
         <v>9.6205583699425765E-2</v>
       </c>
     </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="6"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="6"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="6"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="6"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="6"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="6"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="6"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="6"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B55" s="6"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D17">
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E17">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F17">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G17">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22:D23">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E22:E23">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F23">
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:G23">
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D26:D29">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E26:E29">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26:F29">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G26:G29">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D31:D32">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31:E32">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31:F32">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G31:G32">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D37:D40">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E37:E40">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F37:F40">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G37:G40">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D42:D43">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E42:E43">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F42:F43">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G42:G43">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D47:D50">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E47:E50">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F47:F50">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G47:G50">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D52:D53">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6156,7 +7492,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E17">
+  <conditionalFormatting sqref="E52:E53">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6168,7 +7504,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F17">
+  <conditionalFormatting sqref="F52:F53">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6180,56 +7516,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
+  <conditionalFormatting sqref="G52:G53">
     <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D22:D23">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E22:E23">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22:F23">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G22:G23">
-    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/clustering/sepsectors/sector analysis (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/sector analysis (VDS_s) 0.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="115">
   <si>
     <t>sector</t>
   </si>
@@ -324,6 +324,54 @@
   </si>
   <si>
     <t>43</t>
+  </si>
+  <si>
+    <t>СЕЛЬСКОЕ, ЛЕСНОЕ ХОЗЯЙСТВО, ОХОТА, РЫБОЛОВСТВО И РЫБОВОДСТВО</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>ДОБЫЧА ПОЛЕЗНЫХ ИСКОПАЕМЫХ</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>ОБРАБАТЫВАЮЩИЕ ПРОИЗВОДСТВА</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>СТРОИТЕЛЬСТВО</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>ТОРГОВЛЯ ОПТОВАЯ И РОЗНИЧНАЯ; РЕМОНТ АВТОТРАНСПОРТНЫХ СРЕДСТВ И МОТОЦИКЛОВ</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>ТРАНСПОРТИРОВКА И ХРАНЕНИЕ</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>ДЕЯТЕЛЬНОСТЬ ПРОФЕССИОНАЛЬНАЯ, НАУЧНАЯ И ТЕХНИЧЕСКАЯ</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>ДЕЯТЕЛЬНОСТЬ АДМИНИСТРАТИВНАЯ И СОПУТСТВУЮЩИЕ ДОПОЛНИТЕЛЬНЫЕ УСЛУГИ</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -1387,7 +1435,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B33" s="12"/>
       <c r="C33" s="3">
         <f>AVERAGE(C17:C30)</f>
@@ -1397,120 +1445,237 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="12"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B35" s="12"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B36" s="12"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="12"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="12"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" s="12"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B40" s="12"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B41" s="12"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-    </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B42" s="12"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B43" s="12"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B44" s="12"/>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C36" s="3">
+        <v>4.7030669018119333</v>
+      </c>
+      <c r="D36" s="3">
+        <v>2.8901298438864593</v>
+      </c>
+      <c r="E36" s="3">
+        <v>4.8551022339063907</v>
+      </c>
+      <c r="F36" s="3">
+        <v>0.54338114633168244</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" s="3">
+        <v>3.5865019899753703</v>
+      </c>
+      <c r="D37" s="3">
+        <v>3.2537982636532159</v>
+      </c>
+      <c r="E37" s="3">
+        <v>4.4560052279624465</v>
+      </c>
+      <c r="F37" s="3">
+        <v>1.1593793807464068</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" s="3">
+        <v>2.0103131540352179</v>
+      </c>
+      <c r="D38" s="3">
+        <v>0.93267101567812905</v>
+      </c>
+      <c r="E38" s="3">
+        <v>2.5190872586151345</v>
+      </c>
+      <c r="F38" s="3">
+        <v>1.1555534045986038</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="3">
+        <v>1.4775819198599631</v>
+      </c>
+      <c r="D39" s="3">
+        <v>1.3718824524470641</v>
+      </c>
+      <c r="E39" s="3">
+        <v>1.9764761072330601</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0.6794675155641563</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C40" s="3">
+        <v>6.2067376729116983</v>
+      </c>
+      <c r="D40" s="3">
+        <v>2.9456289391002568</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0.39632604155360068</v>
+      </c>
+      <c r="F40" s="3">
+        <v>1.1022346667896791E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="3">
+        <v>11.796247286330882</v>
+      </c>
+      <c r="D41" s="3">
+        <v>3.3701353993917049</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0.32270229215556578</v>
+      </c>
+      <c r="F41" s="3">
+        <v>0.58794694129813696</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C42" s="3">
+        <v>3.243142089244174</v>
+      </c>
+      <c r="D42" s="3">
+        <v>2.8074620181135077</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0.11140291583466078</v>
+      </c>
+      <c r="F42" s="3">
+        <v>2.3456004945261939</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" s="3">
+        <v>8.8797620553372667</v>
+      </c>
+      <c r="D43" s="3">
+        <v>8.4561035857734002</v>
+      </c>
+      <c r="E43" s="3">
+        <v>9.6999640190591641E-3</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1.469967801891219</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B44" s="13"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B45" s="12"/>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B45" s="13"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B46" s="12"/>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B46" s="13"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B47" s="12"/>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="13"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B48" s="12"/>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="13"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B49" s="12"/>
+      <c r="B49" s="13"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B50" s="12"/>
+      <c r="B50" s="13"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -1572,9 +1737,21 @@
       <c r="F58" s="3"/>
     </row>
   </sheetData>
-  <sortState ref="A2:F30">
-    <sortCondition descending="1" ref="D2:D30"/>
+  <sortState ref="A36:F43">
+    <sortCondition descending="1" ref="E36:E43"/>
   </sortState>
+  <conditionalFormatting sqref="E36:E43">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -4166,7 +4343,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.85546875" customWidth="1"/>
@@ -4455,6 +4632,27 @@
       <c r="G15" s="4">
         <f t="shared" si="1"/>
         <v>8.468050665801991E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17">
+        <f>D14/D15</f>
+        <v>1.4775819198599631</v>
+      </c>
+      <c r="E17">
+        <f t="shared" ref="E17:G17" si="2">E14/E15</f>
+        <v>1.3718824524470641</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="2"/>
+        <v>1.9764761072330601</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="2"/>
+        <v>0.6794675155641563</v>
       </c>
     </row>
   </sheetData>
@@ -4924,6 +5122,24 @@
         <v>4.3731190154563726E-4</v>
       </c>
     </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D20">
+        <f>D17/D18</f>
+        <v>3.243142089244174</v>
+      </c>
+      <c r="E20">
+        <f t="shared" ref="E20:G20" si="2">E17/E18</f>
+        <v>2.8074620181135077</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="2"/>
+        <v>0.11140291583466078</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="2"/>
+        <v>2.3456004945261939</v>
+      </c>
+    </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>83</v>
@@ -5025,15 +5241,15 @@
         <v>4997690.4930611588</v>
       </c>
       <c r="E28" s="3">
-        <f t="shared" ref="E28:G28" si="2">AVERAGE(E23:E24)</f>
+        <f t="shared" ref="E28:G28" si="3">AVERAGE(E23:E24)</f>
         <v>64541.561011874997</v>
       </c>
       <c r="F28" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.6468612366631426E-3</v>
       </c>
       <c r="G28" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.5744933697785639E-4</v>
       </c>
     </row>
@@ -5046,15 +5262,15 @@
         <v>4615790.6120191831</v>
       </c>
       <c r="E29" s="3">
-        <f t="shared" ref="E29:G29" si="3">AVERAGE(E25:E26)</f>
+        <f t="shared" ref="E29:G29" si="4">AVERAGE(E25:E26)</f>
         <v>80571.883507775012</v>
       </c>
       <c r="F29" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.2689735036972318E-3</v>
       </c>
       <c r="G29" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.0298610555049367E-4</v>
       </c>
     </row>
@@ -5067,15 +5283,15 @@
         <v>1.0827376961267559</v>
       </c>
       <c r="E31" s="3">
-        <f t="shared" ref="E31:G31" si="4">E28/E29</f>
+        <f t="shared" ref="E31:G31" si="5">E28/E29</f>
         <v>0.80104322006630113</v>
       </c>
       <c r="F31" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.8738671264906555</v>
       </c>
       <c r="G31" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.1351491544676557</v>
       </c>
     </row>
@@ -6972,6 +7188,27 @@
         <v>9.6205583699425765E-2</v>
       </c>
     </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="2">
+        <f>D22/D23</f>
+        <v>6.2067376729116983</v>
+      </c>
+      <c r="E25" s="2">
+        <f t="shared" ref="E25:G25" si="0">E22/E23</f>
+        <v>2.9456289391002568</v>
+      </c>
+      <c r="F25" s="2">
+        <f t="shared" si="0"/>
+        <v>0.39632604155360068</v>
+      </c>
+      <c r="G25" s="2">
+        <f t="shared" si="0"/>
+        <v>1.1022346667896791E-2</v>
+      </c>
+    </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>

--- a/clustering/sepsectors/sector analysis (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/sector analysis (VDS_s) 0.xlsx
@@ -519,6 +519,1234 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Внутрисекторальная разница'!$C$35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>VDS_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Внутрисекторальная разница'!$B$36:$B$43</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>H</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>C</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>M</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>F</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>B</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>G</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>N</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Внутрисекторальная разница'!$C$36:$C$43</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>4.7030669018119333</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.5865019899753703</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.0103131540352179</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.4775819198599631</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.2067376729116983</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11.796247286330882</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.243142089244174</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.8797620553372667</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-463A-4722-95A8-7F799FEBCB97}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Внутрисекторальная разница'!$D$35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Внутрисекторальная разница'!$B$36:$B$43</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>H</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>C</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>M</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>F</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>B</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>G</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>N</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Внутрисекторальная разница'!$D$36:$D$43</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>2.8901298438864593</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.2537982636532159</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.93267101567812905</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3718824524470641</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.9456289391002568</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.3701353993917049</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.8074620181135077</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.4561035857734002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-463A-4722-95A8-7F799FEBCB97}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Внутрисекторальная разница'!$E$35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Внутрисекторальная разница'!$B$36:$B$43</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>H</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>C</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>M</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>F</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>B</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>G</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>N</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Внутрисекторальная разница'!$E$36:$E$43</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>4.8551022339063907</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.4560052279624465</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.5190872586151345</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.9764761072330601</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.39632604155360068</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.32270229215556578</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.11140291583466078</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.6999640190591641E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-463A-4722-95A8-7F799FEBCB97}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Внутрисекторальная разница'!$F$35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Внутрисекторальная разница'!$B$36:$B$43</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>H</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>C</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>M</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>F</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>B</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>G</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>N</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Внутрисекторальная разница'!$F$36:$F$43</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.54338114633168244</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1593793807464068</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1555534045986038</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.6794675155641563</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1022346667896791E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.58794694129813696</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.3456004945261939</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.469967801891219</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-463A-4722-95A8-7F799FEBCB97}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="330611215"/>
+        <c:axId val="330612463"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="330611215"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="330612463"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="330612463"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="330611215"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>358588</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>101973</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>380999</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>123265</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1754,6 +2982,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/clustering/sepsectors/sector analysis (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/sector analysis (VDS_s) 0.xlsx
@@ -22,6 +22,9 @@
     <sheet name="Административный" sheetId="2" r:id="rId8"/>
     <sheet name="Добыча" sheetId="5" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Внутрисекторальная разница'!$A$1:$F$30</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
@@ -2068,582 +2071,582 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>41</v>
+        <v>65</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="C2" s="3">
-        <v>1.1520246843183004</v>
+        <v>1.1026252311808127</v>
       </c>
       <c r="D2" s="3">
-        <v>2.3213939799145842</v>
+        <v>0.99574889178403025</v>
       </c>
       <c r="E2" s="3">
-        <v>0.80614296667612206</v>
+        <v>44.739847820807242</v>
       </c>
       <c r="F2" s="3">
-        <v>0.25898323939199175</v>
+        <v>0.8055055175801521</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3">
-        <v>1.3517669960910756</v>
+        <v>1.2626658353400688</v>
       </c>
       <c r="D3" s="3">
-        <v>1.9670776981935643</v>
+        <v>0.23138177613322164</v>
       </c>
       <c r="E3" s="3">
-        <v>0.22070836576565364</v>
+        <v>15.780848016319494</v>
       </c>
       <c r="F3" s="3">
-        <v>0.13814015553291181</v>
+        <v>0.9262386419932308</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>82</v>
+        <v>28</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="C4" s="3">
-        <v>1.1917367114224651</v>
+        <v>1.3306477779394272</v>
       </c>
       <c r="D4" s="3">
-        <v>1.9004800470248358</v>
+        <v>0.52497104851926879</v>
       </c>
       <c r="E4" s="3">
-        <v>0.8374708956221617</v>
+        <v>14.558529260558757</v>
       </c>
       <c r="F4" s="3">
-        <v>1.5257452190518532</v>
+        <v>0.20311492992969613</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="C5" s="3">
-        <v>1.0878384484836321</v>
+        <v>1.1171419888702492</v>
       </c>
       <c r="D5" s="3">
-        <v>1.7638605592859029</v>
+        <v>0.74353514130949905</v>
       </c>
       <c r="E5" s="3">
-        <v>0.17960036588529976</v>
+        <v>11.033292593696363</v>
       </c>
       <c r="F5" s="3">
-        <v>1.1305356718336195</v>
+        <v>8.7727411256017351</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>24</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>1.0976688735092679</v>
+        <v>1.1452682356283854</v>
       </c>
       <c r="D6" s="3">
-        <v>1.7109052289159346</v>
+        <v>0.71970300745850779</v>
       </c>
       <c r="E6" s="3">
-        <v>5.1447699646144658</v>
+        <v>6.5995587829731441</v>
       </c>
       <c r="F6" s="3">
-        <v>1.2569187110314528</v>
+        <v>4.1985328533946333</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>39</v>
+        <v>85</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C7" s="3">
-        <v>1.3902001109844437</v>
+        <v>1.0976688735092679</v>
       </c>
       <c r="D7" s="3">
-        <v>1.462361279754929</v>
+        <v>1.7109052289159346</v>
       </c>
       <c r="E7" s="3">
-        <v>0.71207716480109773</v>
+        <v>5.1447699646144658</v>
       </c>
       <c r="F7" s="3">
-        <v>1.2647790839496653</v>
+        <v>1.2569187110314528</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3">
-        <v>1.1404823836685474</v>
+        <v>1.2659566944389276</v>
       </c>
       <c r="D8" s="3">
-        <v>1.2854689383527957</v>
+        <v>1.1816122280015293</v>
       </c>
       <c r="E8" s="3">
-        <v>0.8632074718882139</v>
+        <v>4.0293347314057506</v>
       </c>
       <c r="F8" s="3">
-        <v>2.5147412702861627</v>
+        <v>12.618953438776055</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>75</v>
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>8</v>
       </c>
       <c r="C9" s="3">
-        <v>1.0516922481844897</v>
+        <v>1.2449132022244318</v>
       </c>
       <c r="D9" s="3">
-        <v>1.2423192338416251</v>
+        <v>1.0750082283809359</v>
       </c>
       <c r="E9" s="3">
-        <v>0.40890802664562625</v>
+        <v>3.092669028896593</v>
       </c>
       <c r="F9" s="3">
-        <v>1.7538454461835107</v>
+        <v>1.9048189470819483</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>27</v>
+        <v>83</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="C10" s="3">
-        <v>1.2659566944389276</v>
+        <v>1.0827376961267559</v>
       </c>
       <c r="D10" s="3">
-        <v>1.1816122280015293</v>
+        <v>0.80104322006630113</v>
       </c>
       <c r="E10" s="3">
-        <v>4.0293347314057506</v>
+        <v>2.8738671264906555</v>
       </c>
       <c r="F10" s="3">
-        <v>12.618953438776055</v>
+        <v>1.1351491544676557</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>33</v>
+        <v>89</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C11" s="3">
-        <v>1.2868516961482879</v>
+        <v>1.0557931710621387</v>
       </c>
       <c r="D11" s="3">
-        <v>1.1177412074865631</v>
+        <v>0.59675805501967727</v>
       </c>
       <c r="E11" s="3">
-        <v>0.10176095000792922</v>
+        <v>2.741656360321008</v>
       </c>
       <c r="F11" s="3">
-        <v>1.2821795576565411</v>
+        <v>0.57456911856021375</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="C12" s="3">
-        <v>1.2800215472650383</v>
+        <v>1.116815947298657</v>
       </c>
       <c r="D12" s="3">
-        <v>1.090543283688677</v>
+        <v>0.51990063688275234</v>
       </c>
       <c r="E12" s="3">
-        <v>1.3904082000767517</v>
+        <v>2.5220307584192545</v>
       </c>
       <c r="F12" s="3">
-        <v>1.297125195307224</v>
+        <v>0.22602584912178772</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3">
-        <v>1.2449132022244318</v>
+        <v>1.2833899393849333</v>
       </c>
       <c r="D13" s="3">
-        <v>1.0750082283809359</v>
+        <v>1.0522364209432813</v>
       </c>
       <c r="E13" s="3">
-        <v>3.092669028896593</v>
+        <v>1.6747130060256721</v>
       </c>
       <c r="F13" s="3">
-        <v>1.9048189470819483</v>
+        <v>0.51637317479464306</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="C14" s="3">
-        <v>1.2833899393849333</v>
+        <v>1.0515020276116822</v>
       </c>
       <c r="D14" s="3">
-        <v>1.0522364209432813</v>
+        <v>0.88110216515673767</v>
       </c>
       <c r="E14" s="3">
-        <v>1.6747130060256721</v>
+        <v>1.5793790877321685</v>
       </c>
       <c r="F14" s="3">
-        <v>0.51637317479464306</v>
+        <v>1.5532186573951297</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>45</v>
+        <v>72</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="C15" s="3">
-        <v>1.4503287429709963</v>
+        <v>1.2800215472650383</v>
       </c>
       <c r="D15" s="3">
-        <v>1.0419486207404769</v>
+        <v>1.090543283688677</v>
       </c>
       <c r="E15" s="3">
-        <v>0.6663471741165341</v>
+        <v>1.3904082000767517</v>
       </c>
       <c r="F15" s="3">
-        <v>1.2983469738919464</v>
+        <v>1.297125195307224</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>66</v>
+        <v>22</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="C16" s="3">
-        <v>1.1026252311808127</v>
+        <v>1.2859286844144691</v>
       </c>
       <c r="D16" s="3">
-        <v>0.99574889178403025</v>
+        <v>0.88933632105715787</v>
       </c>
       <c r="E16" s="3">
-        <v>44.739847820807242</v>
+        <v>1.3200782438717298</v>
       </c>
       <c r="F16" s="3">
-        <v>0.8055055175801521</v>
+        <v>0.63162779932699387</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C17" s="3">
-        <v>1.0547425539337831</v>
+        <v>1.1718069796331221</v>
       </c>
       <c r="D17" s="3">
-        <v>0.9009903074402914</v>
+        <v>0.82231497292558131</v>
       </c>
       <c r="E17" s="3">
-        <v>0.59798991148430225</v>
+        <v>1.0066845075285169</v>
       </c>
       <c r="F17" s="3">
-        <v>3.0757485240645135</v>
+        <v>0.95392645329154935</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>23</v>
+        <v>87</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="C18" s="3">
-        <v>1.2859286844144691</v>
+        <v>1.4842736816541999</v>
       </c>
       <c r="D18" s="3">
-        <v>0.88933632105715787</v>
+        <v>0.4121490248256805</v>
       </c>
       <c r="E18" s="3">
-        <v>1.3200782438717298</v>
+        <v>0.96137007040086431</v>
       </c>
       <c r="F18" s="3">
-        <v>0.63162779932699387</v>
+        <v>0.57263086143914699</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C19" s="3">
-        <v>1.0515020276116822</v>
+        <v>1.1404823836685474</v>
       </c>
       <c r="D19" s="3">
-        <v>0.88110216515673767</v>
+        <v>1.2854689383527957</v>
       </c>
       <c r="E19" s="3">
-        <v>1.5793790877321685</v>
+        <v>0.8632074718882139</v>
       </c>
       <c r="F19" s="3">
-        <v>1.5532186573951297</v>
+        <v>2.5147412702861627</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>21</v>
+        <v>81</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="C20" s="3">
-        <v>1.1718069796331221</v>
+        <v>1.1917367114224651</v>
       </c>
       <c r="D20" s="3">
-        <v>0.82231497292558131</v>
+        <v>1.9004800470248358</v>
       </c>
       <c r="E20" s="3">
-        <v>1.0066845075285169</v>
+        <v>0.8374708956221617</v>
       </c>
       <c r="F20" s="3">
-        <v>0.95392645329154935</v>
+        <v>1.5257452190518532</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>84</v>
+        <v>34</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>35</v>
       </c>
       <c r="C21" s="3">
-        <v>1.0827376961267559</v>
+        <v>1.0607758459664012</v>
       </c>
       <c r="D21" s="3">
-        <v>0.80104322006630113</v>
+        <v>0.77167677289668257</v>
       </c>
       <c r="E21" s="3">
-        <v>2.8738671264906555</v>
+        <v>0.82036156049346076</v>
       </c>
       <c r="F21" s="3">
-        <v>1.1351491544676557</v>
+        <v>1.4287748577228767</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C22" s="3">
-        <v>1.0607758459664012</v>
+        <v>1.1520246843183004</v>
       </c>
       <c r="D22" s="3">
-        <v>0.77167677289668257</v>
+        <v>2.3213939799145842</v>
       </c>
       <c r="E22" s="3">
-        <v>0.82036156049346076</v>
+        <v>0.80614296667612206</v>
       </c>
       <c r="F22" s="3">
-        <v>1.4287748577228767</v>
+        <v>0.25898323939199175</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>92</v>
+        <v>38</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="C23" s="3">
-        <v>1.1171419888702492</v>
+        <v>1.3902001109844437</v>
       </c>
       <c r="D23" s="3">
-        <v>0.74353514130949905</v>
+        <v>1.462361279754929</v>
       </c>
       <c r="E23" s="3">
-        <v>11.033292593696363</v>
+        <v>0.71207716480109773</v>
       </c>
       <c r="F23" s="3">
-        <v>8.7727411256017351</v>
+        <v>1.2647790839496653</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C24" s="3">
-        <v>1.1452682356283854</v>
+        <v>1.4503287429709963</v>
       </c>
       <c r="D24" s="3">
-        <v>0.71970300745850779</v>
+        <v>1.0419486207404769</v>
       </c>
       <c r="E24" s="3">
-        <v>6.5995587829731441</v>
+        <v>0.6663471741165341</v>
       </c>
       <c r="F24" s="3">
-        <v>4.1985328533946333</v>
+        <v>1.2983469738919464</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>37</v>
       </c>
       <c r="C25" s="3">
-        <v>1.0557931710621387</v>
+        <v>1.0547425539337831</v>
       </c>
       <c r="D25" s="3">
-        <v>0.59675805501967727</v>
+        <v>0.9009903074402914</v>
       </c>
       <c r="E25" s="3">
-        <v>2.741656360321008</v>
+        <v>0.59798991148430225</v>
       </c>
       <c r="F25" s="3">
-        <v>0.57456911856021375</v>
+        <v>3.0757485240645135</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>29</v>
+        <v>74</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="C26" s="3">
-        <v>1.3306477779394272</v>
+        <v>1.0516922481844897</v>
       </c>
       <c r="D26" s="3">
-        <v>0.52497104851926879</v>
+        <v>1.2423192338416251</v>
       </c>
       <c r="E26" s="3">
-        <v>14.558529260558757</v>
+        <v>0.40890802664562625</v>
       </c>
       <c r="F26" s="3">
-        <v>0.20311492992969613</v>
+        <v>1.7538454461835107</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>56</v>
+        <v>9</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>10</v>
       </c>
       <c r="C27" s="3">
-        <v>1.116815947298657</v>
+        <v>1.3517669960910756</v>
       </c>
       <c r="D27" s="3">
-        <v>0.51990063688275234</v>
+        <v>1.9670776981935643</v>
       </c>
       <c r="E27" s="3">
-        <v>2.5220307584192545</v>
+        <v>0.22070836576565364</v>
       </c>
       <c r="F27" s="3">
-        <v>0.22602584912178772</v>
+        <v>0.13814015553291181</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="C28" s="3">
-        <v>1.2959670995181913</v>
+        <v>1.0878384484836321</v>
       </c>
       <c r="D28" s="3">
-        <v>0.43716192574154161</v>
+        <v>1.7638605592859029</v>
       </c>
       <c r="E28" s="3">
-        <v>6.9063031528892316E-2</v>
+        <v>0.17960036588529976</v>
       </c>
       <c r="F28" s="3">
-        <v>7.525489289467116E-2</v>
+        <v>1.1305356718336195</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>32</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>33</v>
       </c>
       <c r="C29" s="3">
-        <v>1.4842736816541999</v>
+        <v>1.2868516961482879</v>
       </c>
       <c r="D29" s="3">
-        <v>0.4121490248256805</v>
+        <v>1.1177412074865631</v>
       </c>
       <c r="E29" s="3">
-        <v>0.96137007040086431</v>
+        <v>0.10176095000792922</v>
       </c>
       <c r="F29" s="3">
-        <v>0.57263086143914699</v>
+        <v>1.2821795576565411</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>43</v>
+        <v>18</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="C30" s="3">
-        <v>1.2626658353400688</v>
+        <v>1.2959670995181913</v>
       </c>
       <c r="D30" s="3">
-        <v>0.23138177613322164</v>
+        <v>0.43716192574154161</v>
       </c>
       <c r="E30" s="3">
-        <v>15.780848016319494</v>
+        <v>6.9063031528892316E-2</v>
       </c>
       <c r="F30" s="3">
-        <v>0.9262386419932308</v>
+        <v>7.525489289467116E-2</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2657,21 +2660,39 @@
       <c r="B32" s="12"/>
       <c r="C32" s="3">
         <f>AVERAGE(C2:C16)</f>
-        <v>1.2251665006850432</v>
-      </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
+        <v>1.1815384568196832</v>
+      </c>
+      <c r="D32" s="3">
+        <f t="shared" ref="D32:F32" si="0">AVERAGE(D2:D16)</f>
+        <v>0.86758571022116748</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="0"/>
+        <v>7.9387321988139359</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" si="0"/>
+        <v>2.4413942076241701</v>
+      </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B33" s="12"/>
       <c r="C33" s="3">
         <f>AVERAGE(C17:C30)</f>
-        <v>1.1797191089283952</v>
-      </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
+        <v>1.226463441641281</v>
+      </c>
+      <c r="D33" s="3">
+        <f t="shared" ref="D33:F33" si="1">AVERAGE(D17:D30)</f>
+        <v>1.2462103263160755</v>
+      </c>
+      <c r="E33" s="3">
+        <f t="shared" si="1"/>
+        <v>0.58940660448890536</v>
+      </c>
+      <c r="F33" s="3">
+        <f t="shared" si="1"/>
+        <v>1.2338308719422115</v>
+      </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="12"/>
@@ -2965,8 +2986,8 @@
       <c r="F58" s="3"/>
     </row>
   </sheetData>
-  <sortState ref="A36:F43">
-    <sortCondition descending="1" ref="E36:E43"/>
+  <sortState ref="A2:F30">
+    <sortCondition descending="1" ref="E2:E30"/>
   </sortState>
   <conditionalFormatting sqref="E36:E43">
     <cfRule type="colorScale" priority="1">

--- a/clustering/sepsectors/sector analysis (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/sector analysis (VDS_s) 0.xlsx
@@ -2890,17 +2890,41 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B45" s="13"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
+      <c r="C45" s="3">
+        <f>AVERAGE(C36:C39)</f>
+        <v>2.9443659914206215</v>
+      </c>
+      <c r="D45" s="3">
+        <f t="shared" ref="D45:F46" si="2">AVERAGE(D36:D39)</f>
+        <v>2.112120393916217</v>
+      </c>
+      <c r="E45" s="3">
+        <f t="shared" si="2"/>
+        <v>3.4516677069292574</v>
+      </c>
+      <c r="F45" s="3">
+        <f t="shared" si="2"/>
+        <v>0.88444536181021238</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B46" s="13"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
+      <c r="C46" s="3">
+        <f>AVERAGE(C40:C43)</f>
+        <v>7.5314722759560055</v>
+      </c>
+      <c r="D46" s="3">
+        <f t="shared" ref="D46:F46" si="3">AVERAGE(D40:D43)</f>
+        <v>4.3948324855947174</v>
+      </c>
+      <c r="E46" s="3">
+        <f t="shared" si="3"/>
+        <v>0.21003280339072161</v>
+      </c>
+      <c r="F46" s="3">
+        <f t="shared" si="3"/>
+        <v>1.1036343960958617</v>
+      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B47" s="13"/>
@@ -2990,6 +3014,54 @@
     <sortCondition descending="1" ref="E2:E30"/>
   </sortState>
   <conditionalFormatting sqref="E36:E43">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E30">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D30">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F30">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C30">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
